--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127298503</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127297487</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>127298261</v>
       </c>
       <c r="B9" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>127298137</v>
       </c>
       <c r="B14" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R16" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B17" t="n">
-        <v>98353</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R17" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297590</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>97314</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582472</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956480</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,49 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>97320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R20" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97314</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2795,7 +2795,7 @@
         <v>127298842</v>
       </c>
       <c r="B23" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>127298557</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3083,27 +3083,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127297100</v>
+        <v>127298764</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3114,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582502</v>
+        <v>582310</v>
       </c>
       <c r="R26" t="n">
-        <v>6956457</v>
+        <v>6956385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3180,27 +3180,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127298764</v>
+        <v>127297100</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3211,14 +3211,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582310</v>
+        <v>582502</v>
       </c>
       <c r="R27" t="n">
-        <v>6956385</v>
+        <v>6956457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3274,6 +3274,107 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127310220</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skrovellav, Åsens NR,  Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>582296</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6956380</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R7" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,6 +1346,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R16" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R17" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>56840</v>
+        <v>91343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1800,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>91343</v>
+        <v>56840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1897,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R5" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R6" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,39 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R8" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,11 +1351,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298842</v>
+        <v>127298557</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582323</v>
+        <v>582369</v>
       </c>
       <c r="R23" t="n">
-        <v>6956376</v>
+        <v>6956383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R24" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R5" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R6" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R7" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,6 +1346,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>56840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,34 +1800,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B14" t="n">
-        <v>56840</v>
+        <v>91344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,43 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R14" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,45 +2293,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R18" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,49 +2394,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R19" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,39 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R8" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,11 +1351,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>91344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298569</v>
       </c>
       <c r="B13" t="n">
-        <v>56840</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1800,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582347</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>91344</v>
+        <v>56840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1897,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,49 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R18" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,32 +2390,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297682</v>
+        <v>127297590</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>97321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582471</v>
+        <v>582472</v>
       </c>
       <c r="R19" t="n">
-        <v>6956469</v>
+        <v>6956480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,45 +2487,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297590</v>
+        <v>127297973</v>
       </c>
       <c r="B20" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582472</v>
+        <v>582407</v>
       </c>
       <c r="R20" t="n">
-        <v>6956480</v>
+        <v>6956391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298842</v>
+        <v>127297712</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582323</v>
+        <v>582430</v>
       </c>
       <c r="R24" t="n">
-        <v>6956376</v>
+        <v>6956387</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127297712</v>
+        <v>127298842</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582430</v>
+        <v>582323</v>
       </c>
       <c r="R25" t="n">
-        <v>6956387</v>
+        <v>6956376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B12" t="n">
-        <v>91344</v>
+        <v>56840</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,34 +1703,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>91344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299015</v>
+        <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>56840</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,43 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582303</v>
+        <v>582347</v>
       </c>
       <c r="R14" t="n">
-        <v>6956358</v>
+        <v>6956421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R16" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R17" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B5" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R5" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R6" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3083,27 +3083,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127298764</v>
+        <v>127297100</v>
       </c>
       <c r="B26" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3114,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582310</v>
+        <v>582502</v>
       </c>
       <c r="R26" t="n">
-        <v>6956385</v>
+        <v>6956457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3180,27 +3180,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127297100</v>
+        <v>127298764</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3211,14 +3211,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582502</v>
+        <v>582310</v>
       </c>
       <c r="R27" t="n">
-        <v>6956457</v>
+        <v>6956385</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298503</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127297487</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R5" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R6" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,7 +1176,7 @@
         <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,45 +1377,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R9" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1453,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,50 +1484,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R10" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,11 +1555,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,7 +1584,7 @@
         <v>127298049</v>
       </c>
       <c r="B11" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>56840</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,43 +1703,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>56844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,34 +1800,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1898,7 @@
         <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>127298062</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R16" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R17" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>127297590</v>
       </c>
       <c r="B19" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>127297973</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>97325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97321</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R23" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297712</v>
+        <v>127298557</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582430</v>
+        <v>582369</v>
       </c>
       <c r="R24" t="n">
-        <v>6956387</v>
+        <v>6956383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298842</v>
+        <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582323</v>
+        <v>582430</v>
       </c>
       <c r="R25" t="n">
-        <v>6956376</v>
+        <v>6956387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,27 +3083,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127297100</v>
+        <v>127298764</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>80156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3114,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582502</v>
+        <v>582310</v>
       </c>
       <c r="R26" t="n">
-        <v>6956457</v>
+        <v>6956385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3180,27 +3180,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127298764</v>
+        <v>127297100</v>
       </c>
       <c r="B27" t="n">
-        <v>80152</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3211,14 +3211,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582310</v>
+        <v>582502</v>
       </c>
       <c r="R27" t="n">
-        <v>6956385</v>
+        <v>6956457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>127310220</v>
       </c>
       <c r="B28" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R7" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,6 +1346,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,50 +1377,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R9" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,11 +1448,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,45 +1474,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R10" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1555,6 +1550,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>56844</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1800,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1897,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,45 +2293,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R18" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B19" t="n">
-        <v>97325</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2425,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R19" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,49 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R20" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>56844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,34 +1703,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1809,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1833,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>91348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,43 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R14" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,49 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>97325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R18" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B20" t="n">
-        <v>97325</v>
+        <v>80121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R20" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -2293,45 +2293,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297590</v>
+        <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>97325</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582472</v>
+        <v>582407</v>
       </c>
       <c r="R18" t="n">
-        <v>6956480</v>
+        <v>6956391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,49 +2394,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R19" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297682</v>
+        <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>80121</v>
+        <v>97325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582471</v>
+        <v>582472</v>
       </c>
       <c r="R20" t="n">
-        <v>6956469</v>
+        <v>6956480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1377,45 +1377,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R9" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1453,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,50 +1484,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R10" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,11 +1555,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>56844</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,43 +1703,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1897,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>98365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R16" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R17" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>97325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298842</v>
+        <v>127298557</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582323</v>
+        <v>582369</v>
       </c>
       <c r="R23" t="n">
-        <v>6956376</v>
+        <v>6956383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298557</v>
+        <v>127297712</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582369</v>
+        <v>582430</v>
       </c>
       <c r="R24" t="n">
-        <v>6956383</v>
+        <v>6956387</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127297712</v>
+        <v>127298842</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582430</v>
+        <v>582323</v>
       </c>
       <c r="R25" t="n">
-        <v>6956387</v>
+        <v>6956376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,27 +3083,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127298764</v>
+        <v>127297100</v>
       </c>
       <c r="B26" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3114,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582310</v>
+        <v>582502</v>
       </c>
       <c r="R26" t="n">
-        <v>6956385</v>
+        <v>6956457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3180,27 +3180,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127297100</v>
+        <v>127298764</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3211,14 +3211,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582502</v>
+        <v>582310</v>
       </c>
       <c r="R27" t="n">
-        <v>6956457</v>
+        <v>6956385</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -2293,49 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R18" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R23" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297712</v>
+        <v>127298557</v>
       </c>
       <c r="B24" t="n">
         <v>79018</v>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582430</v>
+        <v>582369</v>
       </c>
       <c r="R24" t="n">
-        <v>6956387</v>
+        <v>6956383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298842</v>
+        <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582323</v>
+        <v>582430</v>
       </c>
       <c r="R25" t="n">
-        <v>6956376</v>
+        <v>6956387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298503</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127297487</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B5" t="n">
-        <v>91330</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R5" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R6" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,39 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R8" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,11 +1351,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,50 +1377,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>80152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R9" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,11 +1448,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,45 +1474,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R10" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1555,6 +1550,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,7 +1584,7 @@
         <v>127298049</v>
       </c>
       <c r="B11" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
         <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>127298062</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127297826</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>127298370</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,45 +2293,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R18" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,49 +2394,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>97327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R19" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B20" t="n">
-        <v>97325</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R20" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97325</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>97327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298842</v>
+        <v>127298557</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582323</v>
+        <v>582369</v>
       </c>
       <c r="R23" t="n">
-        <v>6956376</v>
+        <v>6956383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R24" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127297100</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127298764</v>
       </c>
       <c r="B27" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>127310220</v>
       </c>
       <c r="B28" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>91332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R5" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R6" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R7" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,6 +1346,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,45 +1377,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B9" t="n">
-        <v>80152</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R9" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1453,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,50 +1484,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>80152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R10" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,11 +1555,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R16" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R17" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298842</v>
+        <v>127297712</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582323</v>
+        <v>582430</v>
       </c>
       <c r="R24" t="n">
-        <v>6956376</v>
+        <v>6956387</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127297712</v>
+        <v>127298842</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582430</v>
+        <v>582323</v>
       </c>
       <c r="R25" t="n">
-        <v>6956387</v>
+        <v>6956376</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R16" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R17" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,34 +1184,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R7" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1244,6 +1249,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,39 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R8" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,11 +1351,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>56846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,34 +1800,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B14" t="n">
-        <v>56846</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,43 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R14" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127297826</v>
+        <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582438</v>
+        <v>582378</v>
       </c>
       <c r="R16" t="n">
-        <v>6956454</v>
+        <v>6956424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127298370</v>
+        <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582378</v>
+        <v>582438</v>
       </c>
       <c r="R17" t="n">
-        <v>6956424</v>
+        <v>6956454</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,49 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R18" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297590</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582472</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956480</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297682</v>
+        <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>97327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582471</v>
+        <v>582472</v>
       </c>
       <c r="R20" t="n">
-        <v>6956469</v>
+        <v>6956480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>56846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,34 +1703,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>56846</v>
+        <v>91356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R14" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298503</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127297487</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B5" t="n">
-        <v>91338</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R5" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>91341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R6" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,7 +1176,7 @@
         <v>127298468</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127298756</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,50 +1377,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>80155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R9" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,11 +1448,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,45 +1474,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R10" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1555,6 +1550,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,7 +1584,7 @@
         <v>127298049</v>
       </c>
       <c r="B11" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>56846</v>
+        <v>91359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,43 +1703,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1809,34 +1800,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1898,7 @@
         <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>127298062</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,32 +2293,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297682</v>
+        <v>127297590</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>97336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582471</v>
+        <v>582472</v>
       </c>
       <c r="R18" t="n">
-        <v>6956469</v>
+        <v>6956480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,7 +2393,7 @@
         <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>80126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R20" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
         <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R23" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127297712</v>
+        <v>127298557</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582430</v>
+        <v>582369</v>
       </c>
       <c r="R24" t="n">
-        <v>6956387</v>
+        <v>6956383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127298842</v>
+        <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582323</v>
+        <v>582430</v>
       </c>
       <c r="R25" t="n">
-        <v>6956376</v>
+        <v>6956387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3083,27 +3083,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127297100</v>
+        <v>127298764</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>80161</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3114,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582502</v>
+        <v>582310</v>
       </c>
       <c r="R26" t="n">
-        <v>6956457</v>
+        <v>6956385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3180,27 +3180,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127298764</v>
+        <v>127297100</v>
       </c>
       <c r="B27" t="n">
-        <v>80158</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3211,14 +3211,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582310</v>
+        <v>582502</v>
       </c>
       <c r="R27" t="n">
-        <v>6956385</v>
+        <v>6956457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>127310220</v>
       </c>
       <c r="B28" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127298503</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127297487</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>91349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R5" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R6" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127298468</v>
+        <v>127298756</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582359</v>
+        <v>582331</v>
       </c>
       <c r="R7" t="n">
-        <v>6956439</v>
+        <v>6956362</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,11 +1244,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127298756</v>
+        <v>127298468</v>
       </c>
       <c r="B8" t="n">
-        <v>80126</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1281,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582331</v>
+        <v>582359</v>
       </c>
       <c r="R8" t="n">
-        <v>6956362</v>
+        <v>6956439</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,6 +1346,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,7 +1380,7 @@
         <v>127298261</v>
       </c>
       <c r="B9" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>127298472</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>127298049</v>
       </c>
       <c r="B11" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>127298062</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>127298370</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>127297590</v>
       </c>
       <c r="B18" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,49 +2390,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297973</v>
+        <v>127297682</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582407</v>
+        <v>582471</v>
       </c>
       <c r="R19" t="n">
-        <v>6956391</v>
+        <v>6956469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,45 +2487,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B20" t="n">
-        <v>80126</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R20" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>97344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97336</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298842</v>
+        <v>127298557</v>
       </c>
       <c r="B23" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582323</v>
+        <v>582369</v>
       </c>
       <c r="R23" t="n">
-        <v>6956376</v>
+        <v>6956383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R24" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>127297712</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>127298764</v>
       </c>
       <c r="B26" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>127297100</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>127310220</v>
       </c>
       <c r="B28" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127298569</v>
       </c>
       <c r="B12" t="n">
-        <v>91367</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582347</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298137</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>91368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1800,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582411</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298569</v>
+        <v>127299015</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,34 +1897,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582347</v>
+        <v>582303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956421</v>
+        <v>6956358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,32 +2293,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B18" t="n">
-        <v>97344</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R18" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,49 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R20" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2588,45 +2588,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B21" t="n">
-        <v>97344</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R21" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2664,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,50 +2695,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>97345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R22" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2766,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127298557</v>
+        <v>127298842</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582369</v>
+        <v>582323</v>
       </c>
       <c r="R23" t="n">
-        <v>6956383</v>
+        <v>6956376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127298842</v>
+        <v>127298557</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582323</v>
+        <v>582369</v>
       </c>
       <c r="R24" t="n">
-        <v>6956376</v>
+        <v>6956383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R5" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R6" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>91368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R12" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B13" t="n">
-        <v>91368</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,34 +1800,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299015</v>
+        <v>127298569</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>80132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,43 +1906,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582303</v>
+        <v>582347</v>
       </c>
       <c r="R14" t="n">
-        <v>6956358</v>
+        <v>6956421</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,45 +2293,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297682</v>
+        <v>127297973</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582471</v>
+        <v>582407</v>
       </c>
       <c r="R18" t="n">
-        <v>6956469</v>
+        <v>6956391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,49 +2394,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>97345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R19" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127297590</v>
+        <v>127297682</v>
       </c>
       <c r="B20" t="n">
-        <v>97345</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582472</v>
+        <v>582471</v>
       </c>
       <c r="R20" t="n">
-        <v>6956480</v>
+        <v>6956469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 31567-2025 artfynd.xlsx
+++ b/artfynd/A 31567-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127298078</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127297674</v>
+        <v>127298463</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>91351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582430</v>
+        <v>582373</v>
       </c>
       <c r="R5" t="n">
-        <v>6956387</v>
+        <v>6956438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127298463</v>
+        <v>127297674</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582373</v>
+        <v>582430</v>
       </c>
       <c r="R6" t="n">
-        <v>6956438</v>
+        <v>6956387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återkommande inom området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,45 +1377,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127298261</v>
+        <v>127298472</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582388</v>
+        <v>582373</v>
       </c>
       <c r="R9" t="n">
-        <v>6956430</v>
+        <v>6956438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1448,6 +1453,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,50 +1484,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127298472</v>
+        <v>127298261</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582373</v>
+        <v>582388</v>
       </c>
       <c r="R10" t="n">
-        <v>6956438</v>
+        <v>6956430</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,11 +1555,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127298137</v>
+        <v>127299015</v>
       </c>
       <c r="B12" t="n">
-        <v>91368</v>
+        <v>56855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,34 +1703,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582411</v>
+        <v>582303</v>
       </c>
       <c r="R12" t="n">
-        <v>6956413</v>
+        <v>6956358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299015</v>
+        <v>127298569</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1800,43 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582303</v>
+        <v>582347</v>
       </c>
       <c r="R13" t="n">
-        <v>6956358</v>
+        <v>6956421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127298569</v>
+        <v>127298137</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1906,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582347</v>
+        <v>582411</v>
       </c>
       <c r="R14" t="n">
-        <v>6956421</v>
+        <v>6956413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2199,7 @@
         <v>127297826</v>
       </c>
       <c r="B17" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,49 +2293,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127297973</v>
+        <v>127297590</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>97346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Klintarna, Mpd</t>
+          <t>Bjärtbergsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582407</v>
+        <v>582472</v>
       </c>
       <c r="R18" t="n">
-        <v>6956391</v>
+        <v>6956480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,45 +2390,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127297590</v>
+        <v>127297973</v>
       </c>
       <c r="B19" t="n">
-        <v>97345</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjärtbergsbäcken, Mpd</t>
+          <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582472</v>
+        <v>582407</v>
       </c>
       <c r="R19" t="n">
-        <v>6956480</v>
+        <v>6956391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127297795</v>
+        <v>127298684</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>97346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582430</v>
+        <v>582331</v>
       </c>
       <c r="R21" t="n">
-        <v>6956387</v>
+        <v>6956374</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,45 +2685,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127298684</v>
+        <v>127297795</v>
       </c>
       <c r="B22" t="n">
-        <v>97345</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klintarna, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582331</v>
+        <v>582430</v>
       </c>
       <c r="R22" t="n">
-        <v>6956374</v>
+        <v>6956387</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,6 +2761,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
